--- a/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0003_ses-01_WMprob_pdf.xlsx
+++ b/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0003_ses-01_WMprob_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -1069,7 +1070,7 @@
         <v>0.15470650147732015</v>
       </c>
       <c r="D27" s="0">
-        <v>0.024042507152645855</v>
+        <v>0.024042507152645856</v>
       </c>
       <c r="E27" s="0">
         <v>0.037590620245234012</v>
@@ -1250,7 +1251,7 @@
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>2.1586098257359438</v>
+        <v>2.1586098257359439</v>
       </c>
       <c r="B32" s="0">
         <v>4.4736842105263115</v>
@@ -1332,7 +1333,7 @@
         <v>7.0175438596491162</v>
       </c>
       <c r="C34" s="0">
-        <v>4.2354074994610595</v>
+        <v>4.2354074994610596</v>
       </c>
       <c r="D34" s="0">
         <v>2.5869737696246942</v>
@@ -1367,7 +1368,7 @@
         <v>3.8618686620065157</v>
       </c>
       <c r="B35" s="0">
-        <v>6.666666666666698</v>
+        <v>6.6666666666666981</v>
       </c>
       <c r="C35" s="0">
         <v>4.5498928467264577</v>
@@ -1391,7 +1392,7 @@
         <v>4.1071676828662973</v>
       </c>
       <c r="J35" s="0">
-        <v>5.6680161943320106</v>
+        <v>5.6680161943320107</v>
       </c>
       <c r="K35" s="0">
         <v>9.7938144329897359</v>
@@ -1408,7 +1409,7 @@
         <v>5.7017543859649065</v>
       </c>
       <c r="C36" s="0">
-        <v>4.620905667076677</v>
+        <v>4.6209056670766771</v>
       </c>
       <c r="D36" s="0">
         <v>4.7435866612170274</v>
@@ -1478,7 +1479,7 @@
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>3.6428079157231434</v>
+        <v>3.6428079157231435</v>
       </c>
       <c r="B38" s="0">
         <v>5.6140350877192935</v>
@@ -1516,7 +1517,7 @@
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>3.5886580683272586</v>
+        <v>3.5886580683272587</v>
       </c>
       <c r="B39" s="0">
         <v>3.3333333333333304</v>
@@ -1525,7 +1526,7 @@
         <v>4.0464626738862997</v>
       </c>
       <c r="D39" s="0">
-        <v>5.6355636765801886</v>
+        <v>5.6355636765801887</v>
       </c>
       <c r="E39" s="0">
         <v>3.8008293803514395</v>
@@ -1534,7 +1535,7 @@
         <v>3.5803951533675331</v>
       </c>
       <c r="G39" s="0">
-        <v>3.6813518406759171</v>
+        <v>3.6813518406759172</v>
       </c>
       <c r="H39" s="0">
         <v>3.5959779583025586</v>
@@ -1668,7 +1669,7 @@
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>3.1973023530570019</v>
+        <v>3.197302353057002</v>
       </c>
       <c r="B43" s="0">
         <v>1.1403508771929816</v>
@@ -1756,7 +1757,7 @@
         <v>2.8177818382900943</v>
       </c>
       <c r="E45" s="0">
-        <v>3.1617888361824606</v>
+        <v>3.1617888361824607</v>
       </c>
       <c r="F45" s="0">
         <v>2.5470290725175539</v>
@@ -1803,7 +1804,7 @@
         <v>3.1382015691007821</v>
       </c>
       <c r="H46" s="0">
-        <v>3.1528716696017693</v>
+        <v>3.1528716696017694</v>
       </c>
       <c r="I46" s="0">
         <v>3.0068916208218281</v>
@@ -1853,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="L47" s="0">
-        <v>2.6311697197773269</v>
+        <v>2.631169719777327</v>
       </c>
     </row>
     <row r="48">
@@ -1993,7 +1994,7 @@
         <v>1.8507342587004612</v>
       </c>
       <c r="H51" s="0">
-        <v>1.9882974492984133</v>
+        <v>1.9882974492984134</v>
       </c>
       <c r="I51" s="0">
         <v>2.1707612559829972</v>
@@ -2089,7 +2090,7 @@
         <v>2.1413803288372533</v>
       </c>
       <c r="B54" s="0">
-        <v>4.5614035087719262</v>
+        <v>4.5614035087719263</v>
       </c>
       <c r="C54" s="0">
         <v>1.798146058154426</v>
@@ -2177,7 +2178,7 @@
         <v>2.0859810853545731</v>
       </c>
       <c r="F56" s="0">
-        <v>1.6373758323327134</v>
+        <v>1.6373758323327135</v>
       </c>
       <c r="G56" s="0">
         <v>2.0921343794005214</v>
@@ -2367,7 +2368,7 @@
         <v>1.7029147647602836</v>
       </c>
       <c r="F61" s="0">
-        <v>1.2498635520139711</v>
+        <v>1.2498635520139712</v>
       </c>
       <c r="G61" s="0">
         <v>1.3075839871253259</v>
@@ -2385,7 +2386,7 @@
         <v>0.90206185567010222</v>
       </c>
       <c r="L61" s="0">
-        <v>1.2875936926569826</v>
+        <v>1.2875936926569827</v>
       </c>
     </row>
     <row r="62">
@@ -2513,7 +2514,7 @@
         <v>0.94218795571843328</v>
       </c>
       <c r="D65" s="0">
-        <v>0.81263674175943001</v>
+        <v>0.81263674175943002</v>
       </c>
       <c r="E65" s="0">
         <v>1.3031415018347792</v>
@@ -2589,7 +2590,7 @@
         <v>0.83566872519306545</v>
       </c>
       <c r="D67" s="0">
-        <v>0.69482845671146531</v>
+        <v>0.69482845671146532</v>
       </c>
       <c r="E67" s="0">
         <v>1.0978847817655648</v>
@@ -2747,7 +2748,7 @@
         <v>0.78522628956711049</v>
       </c>
       <c r="F71" s="0">
-        <v>0.7568314958337875</v>
+        <v>0.75683149583378751</v>
       </c>
       <c r="G71" s="0">
         <v>0.70408368537517541</v>
@@ -2820,7 +2821,7 @@
         <v>0.33659510013704197</v>
       </c>
       <c r="E73" s="0">
-        <v>0.68558131209164896</v>
+        <v>0.68558131209164897</v>
       </c>
       <c r="F73" s="0">
         <v>0.63311865516864907</v>
@@ -2867,7 +2868,7 @@
         <v>0.78455039227519552</v>
       </c>
       <c r="H74" s="0">
-        <v>0.70442538203715221</v>
+        <v>0.70442538203715222</v>
       </c>
       <c r="I74" s="0">
         <v>0.43494667434609008</v>
@@ -2884,7 +2885,7 @@
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>0.53903711725903269</v>
+        <v>0.5390371172590327</v>
       </c>
       <c r="B75" s="0">
         <v>0.96491228070175361</v>
@@ -2934,7 +2935,7 @@
         <v>0.26206332796383985</v>
       </c>
       <c r="E76" s="0">
-        <v>0.45228079596646636</v>
+        <v>0.45228079596646637</v>
       </c>
       <c r="F76" s="0">
         <v>0.47301968489611723</v>
@@ -2966,7 +2967,7 @@
         <v>0.35087719298245584</v>
       </c>
       <c r="C77" s="0">
-        <v>0.27771085101256648</v>
+        <v>0.27771085101256649</v>
       </c>
       <c r="D77" s="0">
         <v>0.28851008583175031</v>
@@ -2984,7 +2985,7 @@
         <v>0.53968073623814072</v>
       </c>
       <c r="I77" s="0">
-        <v>0.34954618577585322</v>
+        <v>0.34954618577585323</v>
       </c>
       <c r="J77" s="0">
         <v>0.49687154950312801</v>
@@ -3042,7 +3043,7 @@
         <v>0</v>
       </c>
       <c r="C79" s="0">
-        <v>0.20162568635158939</v>
+        <v>0.2016256863515894</v>
       </c>
       <c r="D79" s="0">
         <v>0.26206332796383985</v>
@@ -3244,7 +3245,7 @@
         <v>0.17465342211548943</v>
       </c>
       <c r="G84" s="0">
-        <v>0.24140012070006014</v>
+        <v>0.24140012070006015</v>
       </c>
       <c r="H84" s="0">
         <v>0.2556382434812246</v>
@@ -3323,7 +3324,7 @@
         <v>0.10058338362502504</v>
       </c>
       <c r="H86" s="0">
-        <v>0.18178719536442633</v>
+        <v>0.18178719536442634</v>
       </c>
       <c r="I86" s="0">
         <v>0.10724712518122768</v>
@@ -3437,7 +3438,7 @@
         <v>0.14081673707503506</v>
       </c>
       <c r="H89" s="0">
-        <v>0.090893597682213167</v>
+        <v>0.090893597682213168</v>
       </c>
       <c r="I89" s="0">
         <v>0.053623562590613842</v>
@@ -3487,7 +3488,7 @@
         <v>0.38659793814432958</v>
       </c>
       <c r="L90" s="0">
-        <v>0.04043168600130622</v>
+        <v>0.040431686001306221</v>
       </c>
     </row>
     <row r="91">
@@ -3577,7 +3578,7 @@
         <v>0.0025361721553659039</v>
       </c>
       <c r="D93" s="0">
-        <v>0.024042507152645855</v>
+        <v>0.024042507152645856</v>
       </c>
       <c r="E93" s="0">
         <v>0.0053700886064620016</v>
@@ -3644,7 +3645,7 @@
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B95" s="0">
         <v>0.087719298245613961</v>
@@ -3720,7 +3721,7 @@
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B97" s="0">
         <v>0.087719298245613961</v>
